--- a/feedback_forms/013_hospitality_ai_chatbot_survey--feedback_forms.xlsx
+++ b/feedback_forms/013_hospitality_ai_chatbot_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'chatbot_response'}</t>
+          <t>chatbot_response</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Chatbot Response'}</t>
+          <t>Chatbot Response</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'contextualization'}</t>
+          <t>contextualization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Contextualization'}</t>
+          <t>Contextualization</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'customization'}</t>
+          <t>customization</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Customization'}</t>
+          <t>Customization</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'integration_with_third-party_services'}</t>
+          <t>integration_with_third-party_services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Integration with third-party services'}</t>
+          <t>Integration with third-party services</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'text'}</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Text'}</t>
+          <t>Text</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'voice'}</t>
+          <t>voice</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Voice'}</t>
+          <t>Voice</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'visual'}</t>
+          <t>visual</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Visual'}</t>
+          <t>Visual</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'technical'}</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Technical'}</t>
+          <t>Technical</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'functional'}</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Functional'}</t>
+          <t>Functional</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'user_experience'}</t>
+          <t>user_experience</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'User Experience'}</t>
+          <t>User Experience</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
